--- a/output/pdf_financials_xlsx/MLKM.xlsx
+++ b/output/pdf_financials_xlsx/MLKM.xlsx
@@ -2329,13 +2329,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.025596</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.048796</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.141976</v>
       </c>
     </row>
     <row r="119">
@@ -3611,7 +3611,11 @@
           <t>Exploration and evaluation expenditures (Note 6)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -4124,7 +4128,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>-0.025596</v>
       </c>

--- a/output/pdf_financials_xlsx/MLKM.xlsx
+++ b/output/pdf_financials_xlsx/MLKM.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-3.5e-05</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000113</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.763868</v>
+        <v>-0.763833</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.829917</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.281556</v>
+        <v>-0.281669</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.763868</v>
+        <v>-0.763833</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.829917</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.281556</v>
+        <v>-0.281669</v>
       </c>
     </row>
     <row r="30">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
